--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,7 +426,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -502,7 +502,7 @@
     <t>Extension.value[x].assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -841,7 +841,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -856,7 +856,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="37.421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.1484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-predecessor.xlsx
+++ b/fhir/StructureDefinition-ehealth-predecessor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
